--- a/optaplanner-examples/data/flightcrewscheduling/unsolved/175flights-7days-Europe.xlsx
+++ b/optaplanner-examples/data/flightcrewscheduling/unsolved/175flights-7days-Europe.xlsx
@@ -6724,10 +6724,10 @@
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -6855,7 +6855,7 @@
       <c r="D7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -6864,10 +6864,10 @@
       <c r="G7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="H7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J7" s="2" t="s">
@@ -6980,7 +6980,7 @@
       <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -6989,10 +6989,10 @@
       <c r="F11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="G11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I11" s="2" t="s">
@@ -7007,7 +7007,7 @@
         <v>92</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>18</v>
@@ -7027,7 +7027,7 @@
       <c r="H12" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J12" s="2" t="s">
@@ -7044,7 +7044,7 @@
       <c r="C13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -7056,13 +7056,13 @@
       <c r="G13" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7079,16 +7079,16 @@
       <c r="D14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I14" s="2" t="s">
@@ -7239,13 +7239,13 @@
       <c r="D19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="E19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -7271,10 +7271,10 @@
       <c r="D20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G20" s="2" t="s">
@@ -7286,7 +7286,7 @@
       <c r="I20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
         <v>101</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>18</v>
@@ -7315,10 +7315,10 @@
       <c r="H21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J21" s="2" t="s">
+      <c r="I21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
         <v>103</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
@@ -7437,16 +7437,16 @@
       <c r="F25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       <c r="C26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -7469,7 +7469,7 @@
       <c r="F26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H26" s="2" t="s">
@@ -7487,7 +7487,7 @@
         <v>107</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>18</v>
@@ -7519,7 +7519,7 @@
         <v>108</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>17</v>
@@ -7647,7 +7647,7 @@
         <v>112</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>18</v>
@@ -7655,10 +7655,10 @@
       <c r="D32" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="E32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G32" s="2" t="s">
@@ -7679,7 +7679,7 @@
         <v>113</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>17</v>
@@ -7696,10 +7696,10 @@
       <c r="G33" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I33" s="3" t="s">
+      <c r="H33" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J33" s="2" t="s">
@@ -7711,7 +7711,7 @@
         <v>114</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>17</v>
@@ -7748,7 +7748,7 @@
       <c r="C35" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -7766,7 +7766,7 @@
       <c r="I35" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
         <v>116</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>18</v>
@@ -7789,7 +7789,7 @@
       <c r="F36" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H36" s="2" t="s">
@@ -7847,7 +7847,7 @@
       <c r="D38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F38" s="2" t="s">
@@ -7856,7 +7856,7 @@
       <c r="G38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I38" s="2" t="s">
@@ -7871,7 +7871,7 @@
         <v>119</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>17</v>
@@ -7903,7 +7903,7 @@
         <v>120</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>18</v>
@@ -7935,7 +7935,7 @@
         <v>121</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>18</v>
@@ -7955,7 +7955,7 @@
       <c r="H41" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="I41" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J41" s="2" t="s">
@@ -7999,7 +7999,7 @@
         <v>123</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>17</v>
@@ -8010,16 +8010,16 @@
       <c r="E43" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I43" s="3" t="s">
+      <c r="H43" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I43" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J43" s="2" t="s">
@@ -8031,7 +8031,7 @@
         <v>124</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>17</v>
@@ -8063,27 +8063,27 @@
         <v>125</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G45" s="3" t="s">
+      <c r="F45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I45" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J45" s="2" t="s">
@@ -8095,7 +8095,7 @@
         <v>126</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>18</v>
@@ -8127,7 +8127,7 @@
         <v>127</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>18</v>
@@ -8135,7 +8135,7 @@
       <c r="D47" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F47" s="2" t="s">
@@ -8150,7 +8150,7 @@
       <c r="I47" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="J47" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
@@ -8191,7 +8191,7 @@
         <v>129</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>17</v>
@@ -8223,7 +8223,7 @@
         <v>130</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>18</v>
@@ -8287,24 +8287,24 @@
         <v>132</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="H52" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I52" s="2" t="s">
@@ -8333,7 +8333,7 @@
       <c r="F53" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H53" s="2" t="s">
@@ -8351,7 +8351,7 @@
         <v>134</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>17</v>
@@ -8374,7 +8374,7 @@
       <c r="I54" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J54" s="2" t="s">
+      <c r="J54" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -8388,25 +8388,25 @@
       <c r="C55" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F55" s="3" t="s">
+      <c r="D55" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H55" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="J55" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
         <v>137</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>18</v>
@@ -8502,7 +8502,7 @@
       <c r="I58" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J58" s="2" t="s">
+      <c r="J58" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
         <v>139</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>17</v>
@@ -8543,7 +8543,7 @@
         <v>140</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>18</v>
@@ -8607,7 +8607,7 @@
         <v>142</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>18</v>
@@ -8624,7 +8624,7 @@
       <c r="G62" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="H62" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I62" s="2" t="s">
@@ -8639,7 +8639,7 @@
         <v>143</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>17</v>
@@ -8653,13 +8653,13 @@
       <c r="F63" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I63" s="3" t="s">
+      <c r="I63" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J63" s="2" t="s">
@@ -8688,10 +8688,10 @@
       <c r="G64" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H64" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I64" s="3" t="s">
+      <c r="H64" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I64" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J64" s="2" t="s">
@@ -8708,7 +8708,7 @@
       <c r="C65" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E65" s="2" t="s">
@@ -8717,7 +8717,7 @@
       <c r="F65" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H65" s="2" t="s">
@@ -8735,7 +8735,7 @@
         <v>146</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>18</v>
@@ -8746,7 +8746,7 @@
       <c r="E66" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F66" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G66" s="2" t="s">
@@ -8772,7 +8772,7 @@
       <c r="C67" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E67" s="2" t="s">
@@ -8790,7 +8790,7 @@
       <c r="I67" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="J67" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
         <v>148</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>17</v>
@@ -8839,10 +8839,10 @@
       <c r="D69" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E69" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F69" s="3" t="s">
+      <c r="E69" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G69" s="2" t="s">
@@ -8851,7 +8851,7 @@
       <c r="H69" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I69" s="2" t="s">
+      <c r="I69" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J69" s="2" t="s">
@@ -8863,7 +8863,7 @@
         <v>150</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>18</v>
@@ -8871,7 +8871,7 @@
       <c r="D70" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F70" s="2" t="s">
@@ -8886,7 +8886,7 @@
       <c r="I70" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J70" s="3" t="s">
+      <c r="J70" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -8900,22 +8900,22 @@
       <c r="C71" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E71" s="2" t="s">
+      <c r="D71" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I71" s="3" t="s">
+      <c r="G71" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I71" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J71" s="2" t="s">
@@ -8927,7 +8927,7 @@
         <v>152</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>18</v>
@@ -8959,30 +8959,30 @@
         <v>153</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E73" s="3" t="s">
+      <c r="D73" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="G73" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I73" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J73" s="3" t="s">
+      <c r="I73" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J73" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       <c r="I75" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J75" s="2" t="s">
+      <c r="J75" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -9055,7 +9055,7 @@
         <v>156</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>18</v>
@@ -9066,13 +9066,13 @@
       <c r="E76" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="H76" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I76" s="2" t="s">
@@ -9087,7 +9087,7 @@
         <v>157</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>18</v>
@@ -9119,12 +9119,12 @@
         <v>158</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -9151,7 +9151,7 @@
         <v>159</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>17</v>
@@ -9183,7 +9183,7 @@
         <v>160</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>18</v>
@@ -9215,7 +9215,7 @@
         <v>161</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>18</v>
@@ -9223,7 +9223,7 @@
       <c r="D81" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F81" s="2" t="s">
@@ -9235,7 +9235,7 @@
       <c r="H81" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="I81" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J81" s="2" t="s">
@@ -9247,18 +9247,18 @@
         <v>162</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G82" s="2" t="s">
@@ -9279,7 +9279,7 @@
         <v>163</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>17</v>
@@ -9302,7 +9302,7 @@
       <c r="I83" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="J83" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
         <v>164</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>17</v>
@@ -9343,12 +9343,12 @@
         <v>165</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E85" s="2" t="s">
@@ -9389,7 +9389,7 @@
       <c r="F86" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G86" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H86" s="2" t="s">
@@ -9430,7 +9430,7 @@
       <c r="I87" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J87" s="2" t="s">
+      <c r="J87" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -9447,22 +9447,22 @@
       <c r="D88" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E88" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F88" s="3" t="s">
+      <c r="E88" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H88" s="3" t="s">
+      <c r="H88" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J88" s="3" t="s">
+      <c r="J88" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
         <v>170</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>18</v>
@@ -9514,7 +9514,7 @@
       <c r="E90" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F90" s="2" t="s">
+      <c r="F90" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G90" s="2" t="s">
@@ -9540,13 +9540,13 @@
       <c r="C91" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G91" s="2" t="s">
@@ -9567,7 +9567,7 @@
         <v>172</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>18</v>
@@ -9575,7 +9575,7 @@
       <c r="D92" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F92" s="2" t="s">
@@ -9584,10 +9584,10 @@
       <c r="G92" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H92" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I92" s="2" t="s">
+      <c r="H92" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I92" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J92" s="2" t="s">
@@ -9663,7 +9663,7 @@
         <v>175</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>18</v>
@@ -9671,7 +9671,7 @@
       <c r="D95" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E95" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F95" s="2" t="s">
@@ -9683,10 +9683,10 @@
       <c r="H95" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I95" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J95" s="3" t="s">
+      <c r="I95" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J95" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
         <v>176</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>18</v>
@@ -9727,7 +9727,7 @@
         <v>177</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>18</v>
@@ -9744,7 +9744,7 @@
       <c r="G97" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H97" s="2" t="s">
+      <c r="H97" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I97" s="2" t="s">
@@ -9764,16 +9764,16 @@
       <c r="C98" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E98" s="3" t="s">
+      <c r="D98" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G98" s="3" t="s">
+      <c r="G98" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H98" s="2" t="s">
@@ -9791,7 +9791,7 @@
         <v>179</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>17</v>
@@ -9802,7 +9802,7 @@
       <c r="E99" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G99" s="2" t="s">
@@ -9814,7 +9814,7 @@
       <c r="I99" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J99" s="3" t="s">
+      <c r="J99" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       <c r="D100" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="E100" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F100" s="2" t="s">
@@ -9887,7 +9887,7 @@
         <v>182</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>18</v>
@@ -9910,7 +9910,7 @@
       <c r="I102" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J102" s="2" t="s">
+      <c r="J102" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
         <v>183</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>17</v>
@@ -9965,10 +9965,10 @@
       <c r="F104" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G104" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H104" s="3" t="s">
+      <c r="G104" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H104" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I104" s="2" t="s">
@@ -9983,7 +9983,7 @@
         <v>185</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>18</v>
@@ -10058,7 +10058,7 @@
       <c r="E107" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F107" s="2" t="s">
+      <c r="F107" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G107" s="2" t="s">
@@ -10099,7 +10099,7 @@
       <c r="H108" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I108" s="2" t="s">
+      <c r="I108" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J108" s="2" t="s">
@@ -10143,7 +10143,7 @@
         <v>190</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>18</v>
@@ -10175,12 +10175,12 @@
         <v>191</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D111" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E111" s="2" t="s">
@@ -10195,7 +10195,7 @@
       <c r="H111" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I111" s="3" t="s">
+      <c r="I111" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J111" s="2" t="s">
@@ -10207,7 +10207,7 @@
         <v>192</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>18</v>
@@ -10215,13 +10215,13 @@
       <c r="D112" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E112" s="3" t="s">
+      <c r="E112" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G112" s="3" t="s">
+      <c r="G112" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H112" s="2" t="s">
@@ -10244,7 +10244,7 @@
       <c r="C113" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D113" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E113" s="2" t="s">
@@ -10256,7 +10256,7 @@
       <c r="G113" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H113" s="2" t="s">
+      <c r="H113" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I113" s="2" t="s">
@@ -10335,7 +10335,7 @@
         <v>196</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>18</v>
@@ -10404,22 +10404,22 @@
       <c r="C118" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="D118" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="F118" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H118" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I118" s="3" t="s">
+      <c r="H118" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I118" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J118" s="2" t="s">
@@ -10431,7 +10431,7 @@
         <v>199</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>17</v>
@@ -10495,12 +10495,12 @@
         <v>201</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="D121" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E121" s="2" t="s">
@@ -10518,7 +10518,7 @@
       <c r="I121" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J121" s="3" t="s">
+      <c r="J121" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -10559,7 +10559,7 @@
         <v>203</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>17</v>
@@ -10591,7 +10591,7 @@
         <v>204</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>17</v>
@@ -10695,19 +10695,19 @@
       <c r="D127" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E127" s="3" t="s">
+      <c r="E127" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G127" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I127" s="3" t="s">
+      <c r="G127" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I127" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J127" s="2" t="s">
@@ -10719,7 +10719,7 @@
         <v>208</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>17</v>
@@ -10783,7 +10783,7 @@
         <v>210</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>18</v>
@@ -10797,7 +10797,7 @@
       <c r="F130" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G130" s="2" t="s">
+      <c r="G130" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H130" s="2" t="s">
@@ -10815,7 +10815,7 @@
         <v>211</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>18</v>
@@ -10826,7 +10826,7 @@
       <c r="E131" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F131" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G131" s="2" t="s">
@@ -10835,10 +10835,10 @@
       <c r="H131" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I131" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J131" s="3" t="s">
+      <c r="I131" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J131" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -10847,7 +10847,7 @@
         <v>212</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>18</v>
@@ -10855,7 +10855,7 @@
       <c r="D132" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E132" s="2" t="s">
+      <c r="E132" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F132" s="2" t="s">
@@ -10879,7 +10879,7 @@
         <v>213</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>17</v>
@@ -10948,10 +10948,10 @@
       <c r="C135" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D135" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E135" s="3" t="s">
+      <c r="D135" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F135" s="2" t="s">
@@ -10963,10 +10963,10 @@
       <c r="H135" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I135" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J135" s="3" t="s">
+      <c r="I135" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J135" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -10989,10 +10989,10 @@
       <c r="F136" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G136" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H136" s="3" t="s">
+      <c r="G136" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H136" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I136" s="2" t="s">
@@ -11088,7 +11088,7 @@
       <c r="G139" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H139" s="2" t="s">
+      <c r="H139" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I139" s="2" t="s">
@@ -11103,18 +11103,18 @@
         <v>220</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D140" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F140" s="3" t="s">
+      <c r="D140" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G140" s="2" t="s">
@@ -11146,7 +11146,7 @@
       <c r="E141" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F141" s="2" t="s">
+      <c r="F141" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G141" s="2" t="s">
@@ -11172,7 +11172,7 @@
       <c r="C142" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D142" s="3" t="s">
+      <c r="D142" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E142" s="2" t="s">
@@ -11181,7 +11181,7 @@
       <c r="F142" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G142" s="3" t="s">
+      <c r="G142" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H142" s="2" t="s">
@@ -11263,7 +11263,7 @@
         <v>225</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>18</v>
@@ -11318,7 +11318,7 @@
       <c r="I146" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J146" s="2" t="s">
+      <c r="J146" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
         <v>227</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>18</v>
@@ -11359,7 +11359,7 @@
         <v>228</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>17</v>
@@ -11391,30 +11391,30 @@
         <v>229</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D149" s="3" t="s">
+      <c r="D149" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F149" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G149" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H149" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I149" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J149" s="3" t="s">
+      <c r="F149" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J149" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -16415,7 +16415,7 @@
         <v>92</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -16487,7 +16487,7 @@
         <v>101</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -16503,7 +16503,7 @@
         <v>103</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -16535,7 +16535,7 @@
         <v>107</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -16543,7 +16543,7 @@
         <v>108</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -16575,7 +16575,7 @@
         <v>112</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -16583,7 +16583,7 @@
         <v>113</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
@@ -16591,7 +16591,7 @@
         <v>114</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -16607,7 +16607,7 @@
         <v>116</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37">
@@ -16631,7 +16631,7 @@
         <v>119</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
@@ -16639,7 +16639,7 @@
         <v>120</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -16647,7 +16647,7 @@
         <v>121</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
@@ -16663,7 +16663,7 @@
         <v>123</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
@@ -16671,7 +16671,7 @@
         <v>124</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
@@ -16679,7 +16679,7 @@
         <v>125</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
@@ -16687,7 +16687,7 @@
         <v>126</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
@@ -16695,7 +16695,7 @@
         <v>127</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -16703,7 +16703,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -16711,7 +16711,7 @@
         <v>129</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
@@ -16719,7 +16719,7 @@
         <v>130</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -16735,7 +16735,7 @@
         <v>132</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -16751,7 +16751,7 @@
         <v>134</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -16775,7 +16775,7 @@
         <v>137</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58">
@@ -16791,7 +16791,7 @@
         <v>139</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60">
@@ -16799,7 +16799,7 @@
         <v>140</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -16815,7 +16815,7 @@
         <v>142</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
@@ -16823,7 +16823,7 @@
         <v>143</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64">
@@ -16847,7 +16847,7 @@
         <v>146</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
@@ -16863,7 +16863,7 @@
         <v>148</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
@@ -16879,7 +16879,7 @@
         <v>150</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71">
@@ -16895,7 +16895,7 @@
         <v>152</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
@@ -16903,7 +16903,7 @@
         <v>153</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -16927,7 +16927,7 @@
         <v>156</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77">
@@ -16935,7 +16935,7 @@
         <v>157</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
@@ -16943,7 +16943,7 @@
         <v>158</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
@@ -16951,7 +16951,7 @@
         <v>159</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
@@ -16959,7 +16959,7 @@
         <v>160</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81">
@@ -16967,7 +16967,7 @@
         <v>161</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
@@ -16975,7 +16975,7 @@
         <v>162</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
@@ -16983,7 +16983,7 @@
         <v>163</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84">
@@ -16991,7 +16991,7 @@
         <v>164</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85">
@@ -16999,7 +16999,7 @@
         <v>165</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86">
@@ -17039,7 +17039,7 @@
         <v>170</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91">
@@ -17055,7 +17055,7 @@
         <v>172</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93">
@@ -17079,7 +17079,7 @@
         <v>175</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96">
@@ -17087,7 +17087,7 @@
         <v>176</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97">
@@ -17095,7 +17095,7 @@
         <v>177</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
@@ -17111,7 +17111,7 @@
         <v>179</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
@@ -17135,7 +17135,7 @@
         <v>182</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
@@ -17143,7 +17143,7 @@
         <v>183</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104">
@@ -17159,7 +17159,7 @@
         <v>185</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106">
@@ -17199,7 +17199,7 @@
         <v>190</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111">
@@ -17207,7 +17207,7 @@
         <v>191</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112">
@@ -17215,7 +17215,7 @@
         <v>192</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113">
@@ -17247,7 +17247,7 @@
         <v>196</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117">
@@ -17271,7 +17271,7 @@
         <v>199</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120">
@@ -17287,7 +17287,7 @@
         <v>201</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="122">
@@ -17303,7 +17303,7 @@
         <v>203</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="124">
@@ -17311,7 +17311,7 @@
         <v>204</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125">
@@ -17343,7 +17343,7 @@
         <v>208</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129">
@@ -17359,7 +17359,7 @@
         <v>210</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131">
@@ -17367,7 +17367,7 @@
         <v>211</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132">
@@ -17375,7 +17375,7 @@
         <v>212</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="133">
@@ -17383,7 +17383,7 @@
         <v>213</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134">
@@ -17439,7 +17439,7 @@
         <v>220</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="141">
@@ -17479,7 +17479,7 @@
         <v>225</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="146">
@@ -17495,7 +17495,7 @@
         <v>227</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="148">
@@ -17503,7 +17503,7 @@
         <v>228</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="149">
@@ -17511,7 +17511,7 @@
         <v>229</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="150">

--- a/optaplanner-examples/data/flightcrewscheduling/unsolved/175flights-7days-Europe.xlsx
+++ b/optaplanner-examples/data/flightcrewscheduling/unsolved/175flights-7days-Europe.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3394" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3395" uniqueCount="642">
   <si>
     <t>Schedule start UTC Date</t>
   </si>
@@ -747,6 +747,48 @@
     <t>Employee assignments</t>
   </si>
   <si>
+    <t>AB009</t>
+  </si>
+  <si>
+    <t>2018-01-01 06:17</t>
+  </si>
+  <si>
+    <t>2018-01-01 08:12</t>
+  </si>
+  <si>
+    <t>Pilot, Pilot, Flight attendant, Flight attendant, Flight attendant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">, , , , </t>
+  </si>
+  <si>
+    <t>AB001</t>
+  </si>
+  <si>
+    <t>2018-01-01 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-01 10:02</t>
+  </si>
+  <si>
+    <t>AB023</t>
+  </si>
+  <si>
+    <t>2018-01-01 06:55</t>
+  </si>
+  <si>
+    <t>2018-01-01 10:18</t>
+  </si>
+  <si>
+    <t>AB011</t>
+  </si>
+  <si>
+    <t>2018-01-01 07:02</t>
+  </si>
+  <si>
+    <t>2018-01-01 10:22</t>
+  </si>
+  <si>
     <t>AB003</t>
   </si>
   <si>
@@ -756,10 +798,31 @@
     <t>2018-01-01 10:44</t>
   </si>
   <si>
-    <t>Pilot, Pilot, Flight attendant, Flight attendant, Flight attendant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">, , , , </t>
+    <t>AB007</t>
+  </si>
+  <si>
+    <t>2018-01-01 07:14</t>
+  </si>
+  <si>
+    <t>2018-01-01 09:34</t>
+  </si>
+  <si>
+    <t>AB004</t>
+  </si>
+  <si>
+    <t>2018-01-01 07:26</t>
+  </si>
+  <si>
+    <t>2018-01-01 10:12</t>
+  </si>
+  <si>
+    <t>AB002</t>
+  </si>
+  <si>
+    <t>2018-01-01 08:49</t>
+  </si>
+  <si>
+    <t>2018-01-01 12:12</t>
   </si>
   <si>
     <t>AB008</t>
@@ -771,6 +834,15 @@
     <t>2018-01-01 11:26</t>
   </si>
   <si>
+    <t>AB012</t>
+  </si>
+  <si>
+    <t>2018-01-01 09:12</t>
+  </si>
+  <si>
+    <t>2018-01-01 12:32</t>
+  </si>
+  <si>
     <t>AB021</t>
   </si>
   <si>
@@ -780,6 +852,33 @@
     <t>2018-01-01 12:16</t>
   </si>
   <si>
+    <t>AB020</t>
+  </si>
+  <si>
+    <t>2018-01-01 10:55</t>
+  </si>
+  <si>
+    <t>2018-01-01 14:03</t>
+  </si>
+  <si>
+    <t>AB017</t>
+  </si>
+  <si>
+    <t>2018-01-01 10:57</t>
+  </si>
+  <si>
+    <t>2018-01-01 14:37</t>
+  </si>
+  <si>
+    <t>AB016</t>
+  </si>
+  <si>
+    <t>2018-01-01 11:22</t>
+  </si>
+  <si>
+    <t>2018-01-01 15:02</t>
+  </si>
+  <si>
     <t>AB018</t>
   </si>
   <si>
@@ -789,6 +888,60 @@
     <t>2018-01-01 13:19</t>
   </si>
   <si>
+    <t>AB005</t>
+  </si>
+  <si>
+    <t>2018-01-01 12:53</t>
+  </si>
+  <si>
+    <t>2018-01-01 15:18</t>
+  </si>
+  <si>
+    <t>AB013</t>
+  </si>
+  <si>
+    <t>2018-01-01 13:54</t>
+  </si>
+  <si>
+    <t>2018-01-01 17:34</t>
+  </si>
+  <si>
+    <t>AB014</t>
+  </si>
+  <si>
+    <t>2018-01-01 13:56</t>
+  </si>
+  <si>
+    <t>2018-01-01 17:56</t>
+  </si>
+  <si>
+    <t>AB025</t>
+  </si>
+  <si>
+    <t>2018-01-01 14:44</t>
+  </si>
+  <si>
+    <t>2018-01-01 17:50</t>
+  </si>
+  <si>
+    <t>AB019</t>
+  </si>
+  <si>
+    <t>2018-01-01 14:45</t>
+  </si>
+  <si>
+    <t>2018-01-01 17:45</t>
+  </si>
+  <si>
+    <t>AB010</t>
+  </si>
+  <si>
+    <t>2018-01-01 16:05</t>
+  </si>
+  <si>
+    <t>2018-01-01 18:25</t>
+  </si>
+  <si>
     <t>AB006</t>
   </si>
   <si>
@@ -798,49 +951,13 @@
     <t>2018-01-01 18:47</t>
   </si>
   <si>
-    <t>AB001</t>
-  </si>
-  <si>
-    <t>2018-01-01 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-01 10:02</t>
-  </si>
-  <si>
-    <t>AB023</t>
-  </si>
-  <si>
-    <t>2018-01-01 06:55</t>
-  </si>
-  <si>
-    <t>2018-01-01 10:18</t>
-  </si>
-  <si>
-    <t>AB011</t>
-  </si>
-  <si>
-    <t>2018-01-01 07:02</t>
-  </si>
-  <si>
-    <t>2018-01-01 10:22</t>
-  </si>
-  <si>
-    <t>AB016</t>
-  </si>
-  <si>
-    <t>2018-01-01 11:22</t>
-  </si>
-  <si>
-    <t>2018-01-01 15:02</t>
-  </si>
-  <si>
-    <t>AB013</t>
-  </si>
-  <si>
-    <t>2018-01-01 13:54</t>
-  </si>
-  <si>
-    <t>2018-01-01 17:34</t>
+    <t>AB015</t>
+  </si>
+  <si>
+    <t>2018-01-01 16:50</t>
+  </si>
+  <si>
+    <t>2018-01-01 18:45</t>
   </si>
   <si>
     <t>AB022</t>
@@ -852,96 +969,6 @@
     <t>2018-01-01 19:56</t>
   </si>
   <si>
-    <t>AB015</t>
-  </si>
-  <si>
-    <t>2018-01-01 16:50</t>
-  </si>
-  <si>
-    <t>2018-01-01 18:45</t>
-  </si>
-  <si>
-    <t>AB017</t>
-  </si>
-  <si>
-    <t>2018-01-01 10:57</t>
-  </si>
-  <si>
-    <t>2018-01-01 14:37</t>
-  </si>
-  <si>
-    <t>AB014</t>
-  </si>
-  <si>
-    <t>2018-01-01 13:56</t>
-  </si>
-  <si>
-    <t>2018-01-01 17:56</t>
-  </si>
-  <si>
-    <t>AB012</t>
-  </si>
-  <si>
-    <t>2018-01-01 09:12</t>
-  </si>
-  <si>
-    <t>2018-01-01 12:32</t>
-  </si>
-  <si>
-    <t>AB019</t>
-  </si>
-  <si>
-    <t>2018-01-01 14:45</t>
-  </si>
-  <si>
-    <t>2018-01-01 17:45</t>
-  </si>
-  <si>
-    <t>AB009</t>
-  </si>
-  <si>
-    <t>2018-01-01 06:17</t>
-  </si>
-  <si>
-    <t>2018-01-01 08:12</t>
-  </si>
-  <si>
-    <t>AB005</t>
-  </si>
-  <si>
-    <t>2018-01-01 12:53</t>
-  </si>
-  <si>
-    <t>2018-01-01 15:18</t>
-  </si>
-  <si>
-    <t>AB004</t>
-  </si>
-  <si>
-    <t>2018-01-01 07:26</t>
-  </si>
-  <si>
-    <t>2018-01-01 10:12</t>
-  </si>
-  <si>
-    <t>AB020</t>
-  </si>
-  <si>
-    <t>2018-01-01 10:55</t>
-  </si>
-  <si>
-    <t>2018-01-01 14:03</t>
-  </si>
-  <si>
-    <t>AB002</t>
-  </si>
-  <si>
-    <t>2018-01-01 08:49</t>
-  </si>
-  <si>
-    <t>2018-01-01 12:12</t>
-  </si>
-  <si>
     <t>AB024</t>
   </si>
   <si>
@@ -951,31 +978,28 @@
     <t>2018-01-01 19:37</t>
   </si>
   <si>
-    <t>AB025</t>
-  </si>
-  <si>
-    <t>2018-01-01 14:44</t>
-  </si>
-  <si>
-    <t>2018-01-01 17:50</t>
-  </si>
-  <si>
-    <t>AB007</t>
-  </si>
-  <si>
-    <t>2018-01-01 07:14</t>
-  </si>
-  <si>
-    <t>2018-01-01 09:34</t>
-  </si>
-  <si>
-    <t>AB010</t>
-  </si>
-  <si>
-    <t>2018-01-01 16:05</t>
-  </si>
-  <si>
-    <t>2018-01-01 18:25</t>
+    <t>2018-01-02 06:17</t>
+  </si>
+  <si>
+    <t>2018-01-02 08:12</t>
+  </si>
+  <si>
+    <t>2018-01-02 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-02 10:02</t>
+  </si>
+  <si>
+    <t>2018-01-02 06:55</t>
+  </si>
+  <si>
+    <t>2018-01-02 10:18</t>
+  </si>
+  <si>
+    <t>2018-01-02 07:02</t>
+  </si>
+  <si>
+    <t>2018-01-02 10:22</t>
   </si>
   <si>
     <t>2018-01-02 07:08</t>
@@ -984,58 +1008,112 @@
     <t>2018-01-02 10:44</t>
   </si>
   <si>
+    <t>2018-01-02 07:14</t>
+  </si>
+  <si>
+    <t>2018-01-02 09:34</t>
+  </si>
+  <si>
+    <t>2018-01-02 07:26</t>
+  </si>
+  <si>
+    <t>2018-01-02 10:12</t>
+  </si>
+  <si>
+    <t>2018-01-02 08:49</t>
+  </si>
+  <si>
+    <t>2018-01-02 12:12</t>
+  </si>
+  <si>
     <t>2018-01-02 09:01</t>
   </si>
   <si>
     <t>2018-01-02 11:26</t>
   </si>
   <si>
+    <t>2018-01-02 09:12</t>
+  </si>
+  <si>
+    <t>2018-01-02 12:32</t>
+  </si>
+  <si>
     <t>2018-01-02 09:36</t>
   </si>
   <si>
     <t>2018-01-02 12:16</t>
   </si>
   <si>
+    <t>2018-01-02 10:55</t>
+  </si>
+  <si>
+    <t>2018-01-02 14:03</t>
+  </si>
+  <si>
+    <t>2018-01-02 10:57</t>
+  </si>
+  <si>
+    <t>2018-01-02 14:37</t>
+  </si>
+  <si>
+    <t>2018-01-02 11:22</t>
+  </si>
+  <si>
+    <t>2018-01-02 15:02</t>
+  </si>
+  <si>
     <t>2018-01-02 11:40</t>
   </si>
   <si>
     <t>2018-01-02 13:19</t>
   </si>
   <si>
+    <t>2018-01-02 12:53</t>
+  </si>
+  <si>
+    <t>2018-01-02 15:18</t>
+  </si>
+  <si>
+    <t>2018-01-02 13:54</t>
+  </si>
+  <si>
+    <t>2018-01-02 17:34</t>
+  </si>
+  <si>
+    <t>2018-01-02 13:56</t>
+  </si>
+  <si>
+    <t>2018-01-02 17:56</t>
+  </si>
+  <si>
+    <t>2018-01-02 14:44</t>
+  </si>
+  <si>
+    <t>2018-01-02 17:50</t>
+  </si>
+  <si>
+    <t>2018-01-02 14:45</t>
+  </si>
+  <si>
+    <t>2018-01-02 17:45</t>
+  </si>
+  <si>
+    <t>2018-01-02 16:05</t>
+  </si>
+  <si>
+    <t>2018-01-02 18:25</t>
+  </si>
+  <si>
     <t>2018-01-02 16:27</t>
   </si>
   <si>
     <t>2018-01-02 18:47</t>
   </si>
   <si>
-    <t>2018-01-02 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-02 10:02</t>
-  </si>
-  <si>
-    <t>2018-01-02 06:55</t>
-  </si>
-  <si>
-    <t>2018-01-02 10:18</t>
-  </si>
-  <si>
-    <t>2018-01-02 07:02</t>
-  </si>
-  <si>
-    <t>2018-01-02 10:22</t>
-  </si>
-  <si>
-    <t>2018-01-02 11:22</t>
-  </si>
-  <si>
-    <t>2018-01-02 15:02</t>
-  </si>
-  <si>
-    <t>2018-01-02 13:54</t>
-  </si>
-  <si>
-    <t>2018-01-02 17:34</t>
+    <t>2018-01-02 16:50</t>
+  </si>
+  <si>
+    <t>2018-01-02 18:45</t>
   </si>
   <si>
     <t>2018-01-02 17:16</t>
@@ -1044,88 +1122,34 @@
     <t>2018-01-02 19:56</t>
   </si>
   <si>
-    <t>2018-01-02 16:50</t>
-  </si>
-  <si>
-    <t>2018-01-02 18:45</t>
-  </si>
-  <si>
-    <t>2018-01-02 10:57</t>
-  </si>
-  <si>
-    <t>2018-01-02 14:37</t>
-  </si>
-  <si>
-    <t>2018-01-02 13:56</t>
-  </si>
-  <si>
-    <t>2018-01-02 17:56</t>
-  </si>
-  <si>
-    <t>2018-01-02 09:12</t>
-  </si>
-  <si>
-    <t>2018-01-02 12:32</t>
-  </si>
-  <si>
-    <t>2018-01-02 14:45</t>
-  </si>
-  <si>
-    <t>2018-01-02 17:45</t>
-  </si>
-  <si>
-    <t>2018-01-02 06:17</t>
-  </si>
-  <si>
-    <t>2018-01-02 08:12</t>
-  </si>
-  <si>
-    <t>2018-01-02 12:53</t>
-  </si>
-  <si>
-    <t>2018-01-02 15:18</t>
-  </si>
-  <si>
-    <t>2018-01-02 07:26</t>
-  </si>
-  <si>
-    <t>2018-01-02 10:12</t>
-  </si>
-  <si>
-    <t>2018-01-02 10:55</t>
-  </si>
-  <si>
-    <t>2018-01-02 14:03</t>
-  </si>
-  <si>
-    <t>2018-01-02 08:49</t>
-  </si>
-  <si>
-    <t>2018-01-02 12:12</t>
-  </si>
-  <si>
     <t>2018-01-02 17:44</t>
   </si>
   <si>
     <t>2018-01-02 19:37</t>
   </si>
   <si>
-    <t>2018-01-02 14:44</t>
-  </si>
-  <si>
-    <t>2018-01-02 17:50</t>
-  </si>
-  <si>
-    <t>2018-01-02 07:14</t>
-  </si>
-  <si>
-    <t>2018-01-02 09:34</t>
-  </si>
-  <si>
-    <t>2018-01-02 16:05</t>
-  </si>
-  <si>
-    <t>2018-01-02 18:25</t>
+    <t>2018-01-03 06:17</t>
+  </si>
+  <si>
+    <t>2018-01-03 08:12</t>
+  </si>
+  <si>
+    <t>2018-01-03 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-03 10:02</t>
+  </si>
+  <si>
+    <t>2018-01-03 06:55</t>
+  </si>
+  <si>
+    <t>2018-01-03 10:18</t>
+  </si>
+  <si>
+    <t>2018-01-03 07:02</t>
+  </si>
+  <si>
+    <t>2018-01-03 10:22</t>
   </si>
   <si>
     <t>2018-01-03 07:08</t>
@@ -1134,58 +1158,112 @@
     <t>2018-01-03 10:44</t>
   </si>
   <si>
+    <t>2018-01-03 07:14</t>
+  </si>
+  <si>
+    <t>2018-01-03 09:34</t>
+  </si>
+  <si>
+    <t>2018-01-03 07:26</t>
+  </si>
+  <si>
+    <t>2018-01-03 10:12</t>
+  </si>
+  <si>
+    <t>2018-01-03 08:49</t>
+  </si>
+  <si>
+    <t>2018-01-03 12:12</t>
+  </si>
+  <si>
     <t>2018-01-03 09:01</t>
   </si>
   <si>
     <t>2018-01-03 11:26</t>
   </si>
   <si>
+    <t>2018-01-03 09:12</t>
+  </si>
+  <si>
+    <t>2018-01-03 12:32</t>
+  </si>
+  <si>
     <t>2018-01-03 09:36</t>
   </si>
   <si>
     <t>2018-01-03 12:16</t>
   </si>
   <si>
+    <t>2018-01-03 10:55</t>
+  </si>
+  <si>
+    <t>2018-01-03 14:03</t>
+  </si>
+  <si>
+    <t>2018-01-03 10:57</t>
+  </si>
+  <si>
+    <t>2018-01-03 14:37</t>
+  </si>
+  <si>
+    <t>2018-01-03 11:22</t>
+  </si>
+  <si>
+    <t>2018-01-03 15:02</t>
+  </si>
+  <si>
     <t>2018-01-03 11:40</t>
   </si>
   <si>
     <t>2018-01-03 13:19</t>
   </si>
   <si>
+    <t>2018-01-03 12:53</t>
+  </si>
+  <si>
+    <t>2018-01-03 15:18</t>
+  </si>
+  <si>
+    <t>2018-01-03 13:54</t>
+  </si>
+  <si>
+    <t>2018-01-03 17:34</t>
+  </si>
+  <si>
+    <t>2018-01-03 13:56</t>
+  </si>
+  <si>
+    <t>2018-01-03 17:56</t>
+  </si>
+  <si>
+    <t>2018-01-03 14:44</t>
+  </si>
+  <si>
+    <t>2018-01-03 17:50</t>
+  </si>
+  <si>
+    <t>2018-01-03 14:45</t>
+  </si>
+  <si>
+    <t>2018-01-03 17:45</t>
+  </si>
+  <si>
+    <t>2018-01-03 16:05</t>
+  </si>
+  <si>
+    <t>2018-01-03 18:25</t>
+  </si>
+  <si>
     <t>2018-01-03 16:27</t>
   </si>
   <si>
     <t>2018-01-03 18:47</t>
   </si>
   <si>
-    <t>2018-01-03 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-03 10:02</t>
-  </si>
-  <si>
-    <t>2018-01-03 06:55</t>
-  </si>
-  <si>
-    <t>2018-01-03 10:18</t>
-  </si>
-  <si>
-    <t>2018-01-03 07:02</t>
-  </si>
-  <si>
-    <t>2018-01-03 10:22</t>
-  </si>
-  <si>
-    <t>2018-01-03 11:22</t>
-  </si>
-  <si>
-    <t>2018-01-03 15:02</t>
-  </si>
-  <si>
-    <t>2018-01-03 13:54</t>
-  </si>
-  <si>
-    <t>2018-01-03 17:34</t>
+    <t>2018-01-03 16:50</t>
+  </si>
+  <si>
+    <t>2018-01-03 18:45</t>
   </si>
   <si>
     <t>2018-01-03 17:16</t>
@@ -1194,88 +1272,34 @@
     <t>2018-01-03 19:56</t>
   </si>
   <si>
-    <t>2018-01-03 16:50</t>
-  </si>
-  <si>
-    <t>2018-01-03 18:45</t>
-  </si>
-  <si>
-    <t>2018-01-03 10:57</t>
-  </si>
-  <si>
-    <t>2018-01-03 14:37</t>
-  </si>
-  <si>
-    <t>2018-01-03 13:56</t>
-  </si>
-  <si>
-    <t>2018-01-03 17:56</t>
-  </si>
-  <si>
-    <t>2018-01-03 09:12</t>
-  </si>
-  <si>
-    <t>2018-01-03 12:32</t>
-  </si>
-  <si>
-    <t>2018-01-03 14:45</t>
-  </si>
-  <si>
-    <t>2018-01-03 17:45</t>
-  </si>
-  <si>
-    <t>2018-01-03 06:17</t>
-  </si>
-  <si>
-    <t>2018-01-03 08:12</t>
-  </si>
-  <si>
-    <t>2018-01-03 12:53</t>
-  </si>
-  <si>
-    <t>2018-01-03 15:18</t>
-  </si>
-  <si>
-    <t>2018-01-03 07:26</t>
-  </si>
-  <si>
-    <t>2018-01-03 10:12</t>
-  </si>
-  <si>
-    <t>2018-01-03 10:55</t>
-  </si>
-  <si>
-    <t>2018-01-03 14:03</t>
-  </si>
-  <si>
-    <t>2018-01-03 08:49</t>
-  </si>
-  <si>
-    <t>2018-01-03 12:12</t>
-  </si>
-  <si>
     <t>2018-01-03 17:44</t>
   </si>
   <si>
     <t>2018-01-03 19:37</t>
   </si>
   <si>
-    <t>2018-01-03 14:44</t>
-  </si>
-  <si>
-    <t>2018-01-03 17:50</t>
-  </si>
-  <si>
-    <t>2018-01-03 07:14</t>
-  </si>
-  <si>
-    <t>2018-01-03 09:34</t>
-  </si>
-  <si>
-    <t>2018-01-03 16:05</t>
-  </si>
-  <si>
-    <t>2018-01-03 18:25</t>
+    <t>2018-01-04 06:17</t>
+  </si>
+  <si>
+    <t>2018-01-04 08:12</t>
+  </si>
+  <si>
+    <t>2018-01-04 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-04 10:02</t>
+  </si>
+  <si>
+    <t>2018-01-04 06:55</t>
+  </si>
+  <si>
+    <t>2018-01-04 10:18</t>
+  </si>
+  <si>
+    <t>2018-01-04 07:02</t>
+  </si>
+  <si>
+    <t>2018-01-04 10:22</t>
   </si>
   <si>
     <t>2018-01-04 07:08</t>
@@ -1284,58 +1308,112 @@
     <t>2018-01-04 10:44</t>
   </si>
   <si>
+    <t>2018-01-04 07:14</t>
+  </si>
+  <si>
+    <t>2018-01-04 09:34</t>
+  </si>
+  <si>
+    <t>2018-01-04 07:26</t>
+  </si>
+  <si>
+    <t>2018-01-04 10:12</t>
+  </si>
+  <si>
+    <t>2018-01-04 08:49</t>
+  </si>
+  <si>
+    <t>2018-01-04 12:12</t>
+  </si>
+  <si>
     <t>2018-01-04 09:01</t>
   </si>
   <si>
     <t>2018-01-04 11:26</t>
   </si>
   <si>
+    <t>2018-01-04 09:12</t>
+  </si>
+  <si>
+    <t>2018-01-04 12:32</t>
+  </si>
+  <si>
     <t>2018-01-04 09:36</t>
   </si>
   <si>
     <t>2018-01-04 12:16</t>
   </si>
   <si>
+    <t>2018-01-04 10:55</t>
+  </si>
+  <si>
+    <t>2018-01-04 14:03</t>
+  </si>
+  <si>
+    <t>2018-01-04 10:57</t>
+  </si>
+  <si>
+    <t>2018-01-04 14:37</t>
+  </si>
+  <si>
+    <t>2018-01-04 11:22</t>
+  </si>
+  <si>
+    <t>2018-01-04 15:02</t>
+  </si>
+  <si>
     <t>2018-01-04 11:40</t>
   </si>
   <si>
     <t>2018-01-04 13:19</t>
   </si>
   <si>
+    <t>2018-01-04 12:53</t>
+  </si>
+  <si>
+    <t>2018-01-04 15:18</t>
+  </si>
+  <si>
+    <t>2018-01-04 13:54</t>
+  </si>
+  <si>
+    <t>2018-01-04 17:34</t>
+  </si>
+  <si>
+    <t>2018-01-04 13:56</t>
+  </si>
+  <si>
+    <t>2018-01-04 17:56</t>
+  </si>
+  <si>
+    <t>2018-01-04 14:44</t>
+  </si>
+  <si>
+    <t>2018-01-04 17:50</t>
+  </si>
+  <si>
+    <t>2018-01-04 14:45</t>
+  </si>
+  <si>
+    <t>2018-01-04 17:45</t>
+  </si>
+  <si>
+    <t>2018-01-04 16:05</t>
+  </si>
+  <si>
+    <t>2018-01-04 18:25</t>
+  </si>
+  <si>
     <t>2018-01-04 16:27</t>
   </si>
   <si>
     <t>2018-01-04 18:47</t>
   </si>
   <si>
-    <t>2018-01-04 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-04 10:02</t>
-  </si>
-  <si>
-    <t>2018-01-04 06:55</t>
-  </si>
-  <si>
-    <t>2018-01-04 10:18</t>
-  </si>
-  <si>
-    <t>2018-01-04 07:02</t>
-  </si>
-  <si>
-    <t>2018-01-04 10:22</t>
-  </si>
-  <si>
-    <t>2018-01-04 11:22</t>
-  </si>
-  <si>
-    <t>2018-01-04 15:02</t>
-  </si>
-  <si>
-    <t>2018-01-04 13:54</t>
-  </si>
-  <si>
-    <t>2018-01-04 17:34</t>
+    <t>2018-01-04 16:50</t>
+  </si>
+  <si>
+    <t>2018-01-04 18:45</t>
   </si>
   <si>
     <t>2018-01-04 17:16</t>
@@ -1344,88 +1422,34 @@
     <t>2018-01-04 19:56</t>
   </si>
   <si>
-    <t>2018-01-04 16:50</t>
-  </si>
-  <si>
-    <t>2018-01-04 18:45</t>
-  </si>
-  <si>
-    <t>2018-01-04 10:57</t>
-  </si>
-  <si>
-    <t>2018-01-04 14:37</t>
-  </si>
-  <si>
-    <t>2018-01-04 13:56</t>
-  </si>
-  <si>
-    <t>2018-01-04 17:56</t>
-  </si>
-  <si>
-    <t>2018-01-04 09:12</t>
-  </si>
-  <si>
-    <t>2018-01-04 12:32</t>
-  </si>
-  <si>
-    <t>2018-01-04 14:45</t>
-  </si>
-  <si>
-    <t>2018-01-04 17:45</t>
-  </si>
-  <si>
-    <t>2018-01-04 06:17</t>
-  </si>
-  <si>
-    <t>2018-01-04 08:12</t>
-  </si>
-  <si>
-    <t>2018-01-04 12:53</t>
-  </si>
-  <si>
-    <t>2018-01-04 15:18</t>
-  </si>
-  <si>
-    <t>2018-01-04 07:26</t>
-  </si>
-  <si>
-    <t>2018-01-04 10:12</t>
-  </si>
-  <si>
-    <t>2018-01-04 10:55</t>
-  </si>
-  <si>
-    <t>2018-01-04 14:03</t>
-  </si>
-  <si>
-    <t>2018-01-04 08:49</t>
-  </si>
-  <si>
-    <t>2018-01-04 12:12</t>
-  </si>
-  <si>
     <t>2018-01-04 17:44</t>
   </si>
   <si>
     <t>2018-01-04 19:37</t>
   </si>
   <si>
-    <t>2018-01-04 14:44</t>
-  </si>
-  <si>
-    <t>2018-01-04 17:50</t>
-  </si>
-  <si>
-    <t>2018-01-04 07:14</t>
-  </si>
-  <si>
-    <t>2018-01-04 09:34</t>
-  </si>
-  <si>
-    <t>2018-01-04 16:05</t>
-  </si>
-  <si>
-    <t>2018-01-04 18:25</t>
+    <t>2018-01-05 06:17</t>
+  </si>
+  <si>
+    <t>2018-01-05 08:12</t>
+  </si>
+  <si>
+    <t>2018-01-05 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-05 10:02</t>
+  </si>
+  <si>
+    <t>2018-01-05 06:55</t>
+  </si>
+  <si>
+    <t>2018-01-05 10:18</t>
+  </si>
+  <si>
+    <t>2018-01-05 07:02</t>
+  </si>
+  <si>
+    <t>2018-01-05 10:22</t>
   </si>
   <si>
     <t>2018-01-05 07:08</t>
@@ -1434,58 +1458,112 @@
     <t>2018-01-05 10:44</t>
   </si>
   <si>
+    <t>2018-01-05 07:14</t>
+  </si>
+  <si>
+    <t>2018-01-05 09:34</t>
+  </si>
+  <si>
+    <t>2018-01-05 07:26</t>
+  </si>
+  <si>
+    <t>2018-01-05 10:12</t>
+  </si>
+  <si>
+    <t>2018-01-05 08:49</t>
+  </si>
+  <si>
+    <t>2018-01-05 12:12</t>
+  </si>
+  <si>
     <t>2018-01-05 09:01</t>
   </si>
   <si>
     <t>2018-01-05 11:26</t>
   </si>
   <si>
+    <t>2018-01-05 09:12</t>
+  </si>
+  <si>
+    <t>2018-01-05 12:32</t>
+  </si>
+  <si>
     <t>2018-01-05 09:36</t>
   </si>
   <si>
     <t>2018-01-05 12:16</t>
   </si>
   <si>
+    <t>2018-01-05 10:55</t>
+  </si>
+  <si>
+    <t>2018-01-05 14:03</t>
+  </si>
+  <si>
+    <t>2018-01-05 10:57</t>
+  </si>
+  <si>
+    <t>2018-01-05 14:37</t>
+  </si>
+  <si>
+    <t>2018-01-05 11:22</t>
+  </si>
+  <si>
+    <t>2018-01-05 15:02</t>
+  </si>
+  <si>
     <t>2018-01-05 11:40</t>
   </si>
   <si>
     <t>2018-01-05 13:19</t>
   </si>
   <si>
+    <t>2018-01-05 12:53</t>
+  </si>
+  <si>
+    <t>2018-01-05 15:18</t>
+  </si>
+  <si>
+    <t>2018-01-05 13:54</t>
+  </si>
+  <si>
+    <t>2018-01-05 17:34</t>
+  </si>
+  <si>
+    <t>2018-01-05 13:56</t>
+  </si>
+  <si>
+    <t>2018-01-05 17:56</t>
+  </si>
+  <si>
+    <t>2018-01-05 14:44</t>
+  </si>
+  <si>
+    <t>2018-01-05 17:50</t>
+  </si>
+  <si>
+    <t>2018-01-05 14:45</t>
+  </si>
+  <si>
+    <t>2018-01-05 17:45</t>
+  </si>
+  <si>
+    <t>2018-01-05 16:05</t>
+  </si>
+  <si>
+    <t>2018-01-05 18:25</t>
+  </si>
+  <si>
     <t>2018-01-05 16:27</t>
   </si>
   <si>
     <t>2018-01-05 18:47</t>
   </si>
   <si>
-    <t>2018-01-05 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-05 10:02</t>
-  </si>
-  <si>
-    <t>2018-01-05 06:55</t>
-  </si>
-  <si>
-    <t>2018-01-05 10:18</t>
-  </si>
-  <si>
-    <t>2018-01-05 07:02</t>
-  </si>
-  <si>
-    <t>2018-01-05 10:22</t>
-  </si>
-  <si>
-    <t>2018-01-05 11:22</t>
-  </si>
-  <si>
-    <t>2018-01-05 15:02</t>
-  </si>
-  <si>
-    <t>2018-01-05 13:54</t>
-  </si>
-  <si>
-    <t>2018-01-05 17:34</t>
+    <t>2018-01-05 16:50</t>
+  </si>
+  <si>
+    <t>2018-01-05 18:45</t>
   </si>
   <si>
     <t>2018-01-05 17:16</t>
@@ -1494,88 +1572,34 @@
     <t>2018-01-05 19:56</t>
   </si>
   <si>
-    <t>2018-01-05 16:50</t>
-  </si>
-  <si>
-    <t>2018-01-05 18:45</t>
-  </si>
-  <si>
-    <t>2018-01-05 10:57</t>
-  </si>
-  <si>
-    <t>2018-01-05 14:37</t>
-  </si>
-  <si>
-    <t>2018-01-05 13:56</t>
-  </si>
-  <si>
-    <t>2018-01-05 17:56</t>
-  </si>
-  <si>
-    <t>2018-01-05 09:12</t>
-  </si>
-  <si>
-    <t>2018-01-05 12:32</t>
-  </si>
-  <si>
-    <t>2018-01-05 14:45</t>
-  </si>
-  <si>
-    <t>2018-01-05 17:45</t>
-  </si>
-  <si>
-    <t>2018-01-05 06:17</t>
-  </si>
-  <si>
-    <t>2018-01-05 08:12</t>
-  </si>
-  <si>
-    <t>2018-01-05 12:53</t>
-  </si>
-  <si>
-    <t>2018-01-05 15:18</t>
-  </si>
-  <si>
-    <t>2018-01-05 07:26</t>
-  </si>
-  <si>
-    <t>2018-01-05 10:12</t>
-  </si>
-  <si>
-    <t>2018-01-05 10:55</t>
-  </si>
-  <si>
-    <t>2018-01-05 14:03</t>
-  </si>
-  <si>
-    <t>2018-01-05 08:49</t>
-  </si>
-  <si>
-    <t>2018-01-05 12:12</t>
-  </si>
-  <si>
     <t>2018-01-05 17:44</t>
   </si>
   <si>
     <t>2018-01-05 19:37</t>
   </si>
   <si>
-    <t>2018-01-05 14:44</t>
-  </si>
-  <si>
-    <t>2018-01-05 17:50</t>
-  </si>
-  <si>
-    <t>2018-01-05 07:14</t>
-  </si>
-  <si>
-    <t>2018-01-05 09:34</t>
-  </si>
-  <si>
-    <t>2018-01-05 16:05</t>
-  </si>
-  <si>
-    <t>2018-01-05 18:25</t>
+    <t>2018-01-06 06:17</t>
+  </si>
+  <si>
+    <t>2018-01-06 08:12</t>
+  </si>
+  <si>
+    <t>2018-01-06 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-06 10:02</t>
+  </si>
+  <si>
+    <t>2018-01-06 06:55</t>
+  </si>
+  <si>
+    <t>2018-01-06 10:18</t>
+  </si>
+  <si>
+    <t>2018-01-06 07:02</t>
+  </si>
+  <si>
+    <t>2018-01-06 10:22</t>
   </si>
   <si>
     <t>2018-01-06 07:08</t>
@@ -1584,58 +1608,112 @@
     <t>2018-01-06 10:44</t>
   </si>
   <si>
+    <t>2018-01-06 07:14</t>
+  </si>
+  <si>
+    <t>2018-01-06 09:34</t>
+  </si>
+  <si>
+    <t>2018-01-06 07:26</t>
+  </si>
+  <si>
+    <t>2018-01-06 10:12</t>
+  </si>
+  <si>
+    <t>2018-01-06 08:49</t>
+  </si>
+  <si>
+    <t>2018-01-06 12:12</t>
+  </si>
+  <si>
     <t>2018-01-06 09:01</t>
   </si>
   <si>
     <t>2018-01-06 11:26</t>
   </si>
   <si>
+    <t>2018-01-06 09:12</t>
+  </si>
+  <si>
+    <t>2018-01-06 12:32</t>
+  </si>
+  <si>
     <t>2018-01-06 09:36</t>
   </si>
   <si>
     <t>2018-01-06 12:16</t>
   </si>
   <si>
+    <t>2018-01-06 10:55</t>
+  </si>
+  <si>
+    <t>2018-01-06 14:03</t>
+  </si>
+  <si>
+    <t>2018-01-06 10:57</t>
+  </si>
+  <si>
+    <t>2018-01-06 14:37</t>
+  </si>
+  <si>
+    <t>2018-01-06 11:22</t>
+  </si>
+  <si>
+    <t>2018-01-06 15:02</t>
+  </si>
+  <si>
     <t>2018-01-06 11:40</t>
   </si>
   <si>
     <t>2018-01-06 13:19</t>
   </si>
   <si>
+    <t>2018-01-06 12:53</t>
+  </si>
+  <si>
+    <t>2018-01-06 15:18</t>
+  </si>
+  <si>
+    <t>2018-01-06 13:54</t>
+  </si>
+  <si>
+    <t>2018-01-06 17:34</t>
+  </si>
+  <si>
+    <t>2018-01-06 13:56</t>
+  </si>
+  <si>
+    <t>2018-01-06 17:56</t>
+  </si>
+  <si>
+    <t>2018-01-06 14:44</t>
+  </si>
+  <si>
+    <t>2018-01-06 17:50</t>
+  </si>
+  <si>
+    <t>2018-01-06 14:45</t>
+  </si>
+  <si>
+    <t>2018-01-06 17:45</t>
+  </si>
+  <si>
+    <t>2018-01-06 16:05</t>
+  </si>
+  <si>
+    <t>2018-01-06 18:25</t>
+  </si>
+  <si>
     <t>2018-01-06 16:27</t>
   </si>
   <si>
     <t>2018-01-06 18:47</t>
   </si>
   <si>
-    <t>2018-01-06 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-06 10:02</t>
-  </si>
-  <si>
-    <t>2018-01-06 06:55</t>
-  </si>
-  <si>
-    <t>2018-01-06 10:18</t>
-  </si>
-  <si>
-    <t>2018-01-06 07:02</t>
-  </si>
-  <si>
-    <t>2018-01-06 10:22</t>
-  </si>
-  <si>
-    <t>2018-01-06 11:22</t>
-  </si>
-  <si>
-    <t>2018-01-06 15:02</t>
-  </si>
-  <si>
-    <t>2018-01-06 13:54</t>
-  </si>
-  <si>
-    <t>2018-01-06 17:34</t>
+    <t>2018-01-06 16:50</t>
+  </si>
+  <si>
+    <t>2018-01-06 18:45</t>
   </si>
   <si>
     <t>2018-01-06 17:16</t>
@@ -1644,88 +1722,34 @@
     <t>2018-01-06 19:56</t>
   </si>
   <si>
-    <t>2018-01-06 16:50</t>
-  </si>
-  <si>
-    <t>2018-01-06 18:45</t>
-  </si>
-  <si>
-    <t>2018-01-06 10:57</t>
-  </si>
-  <si>
-    <t>2018-01-06 14:37</t>
-  </si>
-  <si>
-    <t>2018-01-06 13:56</t>
-  </si>
-  <si>
-    <t>2018-01-06 17:56</t>
-  </si>
-  <si>
-    <t>2018-01-06 09:12</t>
-  </si>
-  <si>
-    <t>2018-01-06 12:32</t>
-  </si>
-  <si>
-    <t>2018-01-06 14:45</t>
-  </si>
-  <si>
-    <t>2018-01-06 17:45</t>
-  </si>
-  <si>
-    <t>2018-01-06 06:17</t>
-  </si>
-  <si>
-    <t>2018-01-06 08:12</t>
-  </si>
-  <si>
-    <t>2018-01-06 12:53</t>
-  </si>
-  <si>
-    <t>2018-01-06 15:18</t>
-  </si>
-  <si>
-    <t>2018-01-06 07:26</t>
-  </si>
-  <si>
-    <t>2018-01-06 10:12</t>
-  </si>
-  <si>
-    <t>2018-01-06 10:55</t>
-  </si>
-  <si>
-    <t>2018-01-06 14:03</t>
-  </si>
-  <si>
-    <t>2018-01-06 08:49</t>
-  </si>
-  <si>
-    <t>2018-01-06 12:12</t>
-  </si>
-  <si>
     <t>2018-01-06 17:44</t>
   </si>
   <si>
     <t>2018-01-06 19:37</t>
   </si>
   <si>
-    <t>2018-01-06 14:44</t>
-  </si>
-  <si>
-    <t>2018-01-06 17:50</t>
-  </si>
-  <si>
-    <t>2018-01-06 07:14</t>
-  </si>
-  <si>
-    <t>2018-01-06 09:34</t>
-  </si>
-  <si>
-    <t>2018-01-06 16:05</t>
-  </si>
-  <si>
-    <t>2018-01-06 18:25</t>
+    <t>2018-01-07 06:17</t>
+  </si>
+  <si>
+    <t>2018-01-07 08:12</t>
+  </si>
+  <si>
+    <t>2018-01-07 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-07 10:02</t>
+  </si>
+  <si>
+    <t>2018-01-07 06:55</t>
+  </si>
+  <si>
+    <t>2018-01-07 10:18</t>
+  </si>
+  <si>
+    <t>2018-01-07 07:02</t>
+  </si>
+  <si>
+    <t>2018-01-07 10:22</t>
   </si>
   <si>
     <t>2018-01-07 07:08</t>
@@ -1734,58 +1758,112 @@
     <t>2018-01-07 10:44</t>
   </si>
   <si>
+    <t>2018-01-07 07:14</t>
+  </si>
+  <si>
+    <t>2018-01-07 09:34</t>
+  </si>
+  <si>
+    <t>2018-01-07 07:26</t>
+  </si>
+  <si>
+    <t>2018-01-07 10:12</t>
+  </si>
+  <si>
+    <t>2018-01-07 08:49</t>
+  </si>
+  <si>
+    <t>2018-01-07 12:12</t>
+  </si>
+  <si>
     <t>2018-01-07 09:01</t>
   </si>
   <si>
     <t>2018-01-07 11:26</t>
   </si>
   <si>
+    <t>2018-01-07 09:12</t>
+  </si>
+  <si>
+    <t>2018-01-07 12:32</t>
+  </si>
+  <si>
     <t>2018-01-07 09:36</t>
   </si>
   <si>
     <t>2018-01-07 12:16</t>
   </si>
   <si>
+    <t>2018-01-07 10:55</t>
+  </si>
+  <si>
+    <t>2018-01-07 14:03</t>
+  </si>
+  <si>
+    <t>2018-01-07 10:57</t>
+  </si>
+  <si>
+    <t>2018-01-07 14:37</t>
+  </si>
+  <si>
+    <t>2018-01-07 11:22</t>
+  </si>
+  <si>
+    <t>2018-01-07 15:02</t>
+  </si>
+  <si>
     <t>2018-01-07 11:40</t>
   </si>
   <si>
     <t>2018-01-07 13:19</t>
   </si>
   <si>
+    <t>2018-01-07 12:53</t>
+  </si>
+  <si>
+    <t>2018-01-07 15:18</t>
+  </si>
+  <si>
+    <t>2018-01-07 13:54</t>
+  </si>
+  <si>
+    <t>2018-01-07 17:34</t>
+  </si>
+  <si>
+    <t>2018-01-07 13:56</t>
+  </si>
+  <si>
+    <t>2018-01-07 17:56</t>
+  </si>
+  <si>
+    <t>2018-01-07 14:44</t>
+  </si>
+  <si>
+    <t>2018-01-07 17:50</t>
+  </si>
+  <si>
+    <t>2018-01-07 14:45</t>
+  </si>
+  <si>
+    <t>2018-01-07 17:45</t>
+  </si>
+  <si>
+    <t>2018-01-07 16:05</t>
+  </si>
+  <si>
+    <t>2018-01-07 18:25</t>
+  </si>
+  <si>
     <t>2018-01-07 16:27</t>
   </si>
   <si>
     <t>2018-01-07 18:47</t>
   </si>
   <si>
-    <t>2018-01-07 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-07 10:02</t>
-  </si>
-  <si>
-    <t>2018-01-07 06:55</t>
-  </si>
-  <si>
-    <t>2018-01-07 10:18</t>
-  </si>
-  <si>
-    <t>2018-01-07 07:02</t>
-  </si>
-  <si>
-    <t>2018-01-07 10:22</t>
-  </si>
-  <si>
-    <t>2018-01-07 11:22</t>
-  </si>
-  <si>
-    <t>2018-01-07 15:02</t>
-  </si>
-  <si>
-    <t>2018-01-07 13:54</t>
-  </si>
-  <si>
-    <t>2018-01-07 17:34</t>
+    <t>2018-01-07 16:50</t>
+  </si>
+  <si>
+    <t>2018-01-07 18:45</t>
   </si>
   <si>
     <t>2018-01-07 17:16</t>
@@ -1794,90 +1872,12 @@
     <t>2018-01-07 19:56</t>
   </si>
   <si>
-    <t>2018-01-07 16:50</t>
-  </si>
-  <si>
-    <t>2018-01-07 18:45</t>
-  </si>
-  <si>
-    <t>2018-01-07 10:57</t>
-  </si>
-  <si>
-    <t>2018-01-07 14:37</t>
-  </si>
-  <si>
-    <t>2018-01-07 13:56</t>
-  </si>
-  <si>
-    <t>2018-01-07 17:56</t>
-  </si>
-  <si>
-    <t>2018-01-07 09:12</t>
-  </si>
-  <si>
-    <t>2018-01-07 12:32</t>
-  </si>
-  <si>
-    <t>2018-01-07 14:45</t>
-  </si>
-  <si>
-    <t>2018-01-07 17:45</t>
-  </si>
-  <si>
-    <t>2018-01-07 06:17</t>
-  </si>
-  <si>
-    <t>2018-01-07 08:12</t>
-  </si>
-  <si>
-    <t>2018-01-07 12:53</t>
-  </si>
-  <si>
-    <t>2018-01-07 15:18</t>
-  </si>
-  <si>
-    <t>2018-01-07 07:26</t>
-  </si>
-  <si>
-    <t>2018-01-07 10:12</t>
-  </si>
-  <si>
-    <t>2018-01-07 10:55</t>
-  </si>
-  <si>
-    <t>2018-01-07 14:03</t>
-  </si>
-  <si>
-    <t>2018-01-07 08:49</t>
-  </si>
-  <si>
-    <t>2018-01-07 12:12</t>
-  </si>
-  <si>
     <t>2018-01-07 17:44</t>
   </si>
   <si>
     <t>2018-01-07 19:37</t>
   </si>
   <si>
-    <t>2018-01-07 14:44</t>
-  </si>
-  <si>
-    <t>2018-01-07 17:50</t>
-  </si>
-  <si>
-    <t>2018-01-07 07:14</t>
-  </si>
-  <si>
-    <t>2018-01-07 09:34</t>
-  </si>
-  <si>
-    <t>2018-01-07 16:05</t>
-  </si>
-  <si>
-    <t>2018-01-07 18:25</t>
-  </si>
-  <si>
     <t>Employee name</t>
   </si>
   <si>
@@ -1929,19 +1929,22 @@
     <t>-875init</t>
   </si>
   <si>
-    <t>Constraint match</t>
+    <t>Constraint name</t>
+  </si>
+  <si>
+    <t>Constraint weight</t>
+  </si>
+  <si>
+    <t>Match count</t>
   </si>
   <si>
     <t>Match score</t>
   </si>
   <si>
-    <t>Total score</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    </t>
+    <t>Justifications</t>
+  </si>
+  <si>
+    <t>Unassigned variables</t>
   </si>
 </sst>
 </file>
@@ -1963,7 +1966,7 @@
       <b val="true"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1972,6 +1975,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="BABDB6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1998,6 +2006,16 @@
         <fgColor rgb="FCAF3E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FCE94F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2011,30 +2029,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyFont="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment wrapText="true" vertical="center" horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment wrapText="true" vertical="center" horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2075,12 +2105,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="15.99609375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="114.34375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="14.91015625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="113.4453125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2175,10 +2205,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="14.7265625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2204,13 +2234,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="6.22265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="6.48828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.51171875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="5.67578125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="6.4140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.83984375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.2890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2935,60 +2965,60 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="12.5078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="4.9609375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="4.609375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="5.0078125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="5.3515625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.63671875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.37890625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="5.6953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="4.90234375" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="5.37890625" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="5.578125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="4.71484375" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="4.8828125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="4.921875" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="5.4375" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="5.109375" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="4.71875" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="4.77734375" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="4.734375" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="5.7578125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="4.51171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="4.37890625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="4.6328125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="4.91796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="4.37890625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.359375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="4.86328125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="4.37890625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="4.4453125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="4.9609375" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="5.046875" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="5.69921875" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="5.08984375" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="4.4453125" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="4.5234375" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="6.375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="4.8671875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="4.48046875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="4.37890625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="4.7421875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="5.109375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="4.88671875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="4.37890625" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="4.80078125" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="5.0703125" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="4.83203125" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="4.421875" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="5.19921875" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="4.66015625" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="4.59375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="12.33203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="4.859375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="4.6484375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="5.01953125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="5.02734375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.44921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.10546875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="5.359375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="4.9296875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="5.1875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="5.34765625" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="4.73046875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="4.7265625" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="4.796875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="5.20703125" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="5.05859375" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="4.69140625" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="4.8125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="5.4140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="4.5859375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="4.10546875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="4.89453125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="4.60546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="4.87109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="4.10546875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.03515625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="4.73828125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="4.2421875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="4.52734375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="4.8046875" customWidth="true" bestFit="true"/>
+    <col min="32" max="32" width="4.85546875" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" width="5.37890625" customWidth="true" bestFit="true"/>
+    <col min="34" max="34" width="4.79296875" customWidth="true" bestFit="true"/>
+    <col min="35" max="35" width="4.50390625" customWidth="true" bestFit="true"/>
+    <col min="36" max="36" width="4.5625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="5.76953125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="4.7734375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="4.4765625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="4.16796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="4.7578125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="5.05859375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="4.8125" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="4.21875" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="4.74609375" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="47" max="47" width="4.75" customWidth="true" bestFit="true"/>
+    <col min="48" max="48" width="4.35546875" customWidth="true" bestFit="true"/>
+    <col min="49" max="49" width="5.16015625" customWidth="true" bestFit="true"/>
+    <col min="50" max="50" width="4.625" customWidth="true" bestFit="true"/>
+    <col min="51" max="51" width="4.46484375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6666,7 +6696,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="1">
     <mergeCell ref="A1:U1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -6676,19 +6706,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="14.765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.3359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.36328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="16.10546875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="15.1953125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="16.1015625" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="15.26953125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.15234375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.70703125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="15.21875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="14.12890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.25390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.7265625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="14.9921875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="15.671875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="15.09375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.98828125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="14.50390625" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="15.078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6753,7 +6783,7 @@
       <c r="E3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>76</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -6765,7 +6795,7 @@
       <c r="I3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -6878,7 +6908,7 @@
       <c r="D7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="5" t="s">
         <v>76</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -7003,7 +7033,7 @@
       <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -7050,7 +7080,7 @@
       <c r="H12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="5" t="s">
         <v>76</v>
       </c>
       <c r="J12" s="2" t="s">
@@ -7076,10 +7106,10 @@
       <c r="F13" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="3" t="s">
+      <c r="G13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I13" s="2" t="s">
@@ -7111,7 +7141,7 @@
       <c r="G14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I14" s="2" t="s">
@@ -7265,7 +7295,7 @@
       <c r="E19" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="5" t="s">
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
@@ -7294,7 +7324,7 @@
       <c r="D20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="5" t="s">
         <v>76</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -7323,7 +7353,7 @@
       <c r="C21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -7341,7 +7371,7 @@
       <c r="I21" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -7460,13 +7490,13 @@
       <c r="F25" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="5" t="s">
         <v>76</v>
       </c>
       <c r="J25" s="2" t="s">
@@ -7812,7 +7842,7 @@
       <c r="F36" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H36" s="2" t="s">
@@ -7978,7 +8008,7 @@
       <c r="H41" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="5" t="s">
         <v>76</v>
       </c>
       <c r="J41" s="2" t="s">
@@ -8039,7 +8069,7 @@
       <c r="G43" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H43" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I43" s="2" t="s">
@@ -8091,7 +8121,7 @@
       <c r="C45" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E45" s="2" t="s">
@@ -8321,7 +8351,7 @@
       <c r="E52" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="5" t="s">
         <v>76</v>
       </c>
       <c r="G52" s="2" t="s">
@@ -8350,7 +8380,7 @@
       <c r="D53" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="5" t="s">
         <v>76</v>
       </c>
       <c r="F53" s="2" t="s">
@@ -8397,7 +8427,7 @@
       <c r="I54" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J54" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -8414,7 +8444,7 @@
       <c r="D55" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" s="5" t="s">
         <v>76</v>
       </c>
       <c r="F55" s="2" t="s">
@@ -8525,7 +8555,7 @@
       <c r="I58" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="J58" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -8647,7 +8677,7 @@
       <c r="G62" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H62" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I62" s="2" t="s">
@@ -8731,7 +8761,7 @@
       <c r="C65" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E65" s="2" t="s">
@@ -8740,7 +8770,7 @@
       <c r="F65" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H65" s="2" t="s">
@@ -8769,7 +8799,7 @@
       <c r="E66" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="5" t="s">
         <v>76</v>
       </c>
       <c r="G66" s="2" t="s">
@@ -8874,7 +8904,7 @@
       <c r="H69" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I69" s="3" t="s">
+      <c r="I69" s="5" t="s">
         <v>76</v>
       </c>
       <c r="J69" s="2" t="s">
@@ -8926,7 +8956,7 @@
       <c r="D71" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" s="5" t="s">
         <v>76</v>
       </c>
       <c r="F71" s="2" t="s">
@@ -8993,7 +9023,7 @@
       <c r="E73" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="5" t="s">
         <v>76</v>
       </c>
       <c r="G73" s="2" t="s">
@@ -9069,7 +9099,7 @@
       <c r="I75" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J75" s="3" t="s">
+      <c r="J75" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -9147,7 +9177,7 @@
       <c r="C78" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -9319,7 +9349,7 @@
       <c r="G83" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="H83" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I83" s="2" t="s">
@@ -9348,7 +9378,7 @@
       <c r="F84" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G84" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H84" s="2" t="s">
@@ -9386,7 +9416,7 @@
       <c r="H85" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I85" s="3" t="s">
+      <c r="I85" s="5" t="s">
         <v>76</v>
       </c>
       <c r="J85" s="2" t="s">
@@ -9412,7 +9442,7 @@
       <c r="F86" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="G86" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H86" s="2" t="s">
@@ -9453,7 +9483,7 @@
       <c r="I87" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J87" s="3" t="s">
+      <c r="J87" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -9537,7 +9567,7 @@
       <c r="E90" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="5" t="s">
         <v>76</v>
       </c>
       <c r="G90" s="2" t="s">
@@ -9610,7 +9640,7 @@
       <c r="H92" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I92" s="3" t="s">
+      <c r="I92" s="5" t="s">
         <v>76</v>
       </c>
       <c r="J92" s="2" t="s">
@@ -9694,7 +9724,7 @@
       <c r="D95" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" s="5" t="s">
         <v>76</v>
       </c>
       <c r="F95" s="2" t="s">
@@ -9767,7 +9797,7 @@
       <c r="G97" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H97" s="3" t="s">
+      <c r="H97" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I97" s="2" t="s">
@@ -9787,7 +9817,7 @@
       <c r="C98" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E98" s="2" t="s">
@@ -9854,7 +9884,7 @@
       <c r="D100" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="5" t="s">
         <v>76</v>
       </c>
       <c r="F100" s="2" t="s">
@@ -9933,7 +9963,7 @@
       <c r="I102" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J102" s="3" t="s">
+      <c r="J102" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -10081,7 +10111,7 @@
       <c r="E107" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F107" s="5" t="s">
         <v>76</v>
       </c>
       <c r="G107" s="2" t="s">
@@ -10122,7 +10152,7 @@
       <c r="H108" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I108" s="3" t="s">
+      <c r="I108" s="5" t="s">
         <v>76</v>
       </c>
       <c r="J108" s="2" t="s">
@@ -10267,7 +10297,7 @@
       <c r="C113" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E113" s="2" t="s">
@@ -10279,7 +10309,7 @@
       <c r="G113" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H113" s="3" t="s">
+      <c r="H113" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I113" s="2" t="s">
@@ -10820,7 +10850,7 @@
       <c r="F130" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G130" s="3" t="s">
+      <c r="G130" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H130" s="2" t="s">
@@ -10858,7 +10888,7 @@
       <c r="H131" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I131" s="3" t="s">
+      <c r="I131" s="5" t="s">
         <v>76</v>
       </c>
       <c r="J131" s="2" t="s">
@@ -10878,7 +10908,7 @@
       <c r="D132" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E132" s="3" t="s">
+      <c r="E132" s="5" t="s">
         <v>76</v>
       </c>
       <c r="F132" s="2" t="s">
@@ -11111,7 +11141,7 @@
       <c r="G139" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="H139" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I139" s="2" t="s">
@@ -11131,7 +11161,7 @@
       <c r="C140" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D140" s="3" t="s">
+      <c r="D140" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E140" s="2" t="s">
@@ -11169,7 +11199,7 @@
       <c r="E141" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F141" s="3" t="s">
+      <c r="F141" s="5" t="s">
         <v>76</v>
       </c>
       <c r="G141" s="2" t="s">
@@ -11341,7 +11371,7 @@
       <c r="I146" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J146" s="3" t="s">
+      <c r="J146" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -11545,16 +11575,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G176"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="13.84765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="22.1328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.94921875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="18.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.6796875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="56.2890625" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="21.8984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.8984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="22.05078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.71484375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="18.65625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="20.3203125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="53.78125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="21.96484375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11585,13 +11615,13 @@
         <v>242</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>244</v>
@@ -11608,13 +11638,13 @@
         <v>247</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>248</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>249</v>
@@ -11631,13 +11661,13 @@
         <v>250</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>251</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>252</v>
@@ -11654,13 +11684,13 @@
         <v>253</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>254</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>255</v>
@@ -11683,7 +11713,7 @@
         <v>257</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>258</v>
@@ -11700,13 +11730,13 @@
         <v>259</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>260</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>261</v>
@@ -11723,13 +11753,13 @@
         <v>262</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>263</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>264</v>
@@ -11746,13 +11776,13 @@
         <v>265</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>266</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>267</v>
@@ -11769,13 +11799,13 @@
         <v>268</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>269</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>270</v>
@@ -11792,13 +11822,13 @@
         <v>271</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>272</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>273</v>
@@ -11815,13 +11845,13 @@
         <v>274</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>275</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>276</v>
@@ -11838,13 +11868,13 @@
         <v>277</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>278</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>279</v>
@@ -11884,13 +11914,13 @@
         <v>283</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>284</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>285</v>
@@ -11907,13 +11937,13 @@
         <v>286</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>287</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>288</v>
@@ -11930,13 +11960,13 @@
         <v>289</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>290</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>291</v>
@@ -11953,13 +11983,13 @@
         <v>292</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>293</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>294</v>
@@ -11976,13 +12006,13 @@
         <v>295</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>296</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>297</v>
@@ -11999,13 +12029,13 @@
         <v>298</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>299</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>300</v>
@@ -12022,13 +12052,13 @@
         <v>301</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>302</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>303</v>
@@ -12045,13 +12075,13 @@
         <v>304</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>305</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>306</v>
@@ -12068,13 +12098,13 @@
         <v>307</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>308</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>309</v>
@@ -12091,7 +12121,7 @@
         <v>310</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>311</v>
@@ -12114,7 +12144,7 @@
         <v>313</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>314</v>
@@ -12137,13 +12167,13 @@
         <v>316</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>317</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>318</v>
@@ -12160,13 +12190,13 @@
         <v>242</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>319</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>320</v>
@@ -12183,13 +12213,13 @@
         <v>247</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>322</v>
@@ -12206,13 +12236,13 @@
         <v>250</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>323</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>324</v>
@@ -12229,13 +12259,13 @@
         <v>253</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>325</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>326</v>
@@ -12258,7 +12288,7 @@
         <v>327</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>328</v>
@@ -12275,13 +12305,13 @@
         <v>259</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>329</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>330</v>
@@ -12298,13 +12328,13 @@
         <v>262</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>331</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>332</v>
@@ -12321,13 +12351,13 @@
         <v>265</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>333</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>334</v>
@@ -12344,13 +12374,13 @@
         <v>268</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>335</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>336</v>
@@ -12367,13 +12397,13 @@
         <v>271</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>337</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>338</v>
@@ -12390,13 +12420,13 @@
         <v>274</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>340</v>
@@ -12413,13 +12443,13 @@
         <v>277</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>341</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>342</v>
@@ -12459,13 +12489,13 @@
         <v>283</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>345</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>346</v>
@@ -12482,13 +12512,13 @@
         <v>286</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>347</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>348</v>
@@ -12505,13 +12535,13 @@
         <v>289</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>349</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>350</v>
@@ -12528,13 +12558,13 @@
         <v>292</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>351</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>352</v>
@@ -12551,13 +12581,13 @@
         <v>295</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>353</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>354</v>
@@ -12574,13 +12604,13 @@
         <v>298</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>355</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>356</v>
@@ -12597,13 +12627,13 @@
         <v>301</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>357</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>358</v>
@@ -12620,13 +12650,13 @@
         <v>304</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>359</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>360</v>
@@ -12643,13 +12673,13 @@
         <v>307</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>361</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>362</v>
@@ -12666,7 +12696,7 @@
         <v>310</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>363</v>
@@ -12689,7 +12719,7 @@
         <v>313</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>365</v>
@@ -12712,13 +12742,13 @@
         <v>316</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>368</v>
@@ -12735,13 +12765,13 @@
         <v>242</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>369</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>370</v>
@@ -12758,13 +12788,13 @@
         <v>247</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>371</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>372</v>
@@ -12781,13 +12811,13 @@
         <v>250</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>373</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>374</v>
@@ -12804,13 +12834,13 @@
         <v>253</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>375</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>376</v>
@@ -12833,7 +12863,7 @@
         <v>377</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>378</v>
@@ -12850,13 +12880,13 @@
         <v>259</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>379</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>380</v>
@@ -12873,13 +12903,13 @@
         <v>262</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>381</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>382</v>
@@ -12896,13 +12926,13 @@
         <v>265</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>383</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>384</v>
@@ -12919,13 +12949,13 @@
         <v>268</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>385</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>386</v>
@@ -12942,13 +12972,13 @@
         <v>271</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>387</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>388</v>
@@ -12965,13 +12995,13 @@
         <v>274</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>389</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>390</v>
@@ -12988,13 +13018,13 @@
         <v>277</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>391</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>392</v>
@@ -13034,13 +13064,13 @@
         <v>283</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>395</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>396</v>
@@ -13057,13 +13087,13 @@
         <v>286</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>397</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>398</v>
@@ -13080,13 +13110,13 @@
         <v>289</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>399</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>400</v>
@@ -13103,13 +13133,13 @@
         <v>292</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>401</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>402</v>
@@ -13126,13 +13156,13 @@
         <v>295</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>403</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>404</v>
@@ -13149,13 +13179,13 @@
         <v>298</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>405</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>406</v>
@@ -13172,13 +13202,13 @@
         <v>301</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>407</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>408</v>
@@ -13195,13 +13225,13 @@
         <v>304</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>409</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>410</v>
@@ -13218,13 +13248,13 @@
         <v>307</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>411</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>412</v>
@@ -13241,7 +13271,7 @@
         <v>310</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>413</v>
@@ -13264,7 +13294,7 @@
         <v>313</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>415</v>
@@ -13287,13 +13317,13 @@
         <v>316</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>417</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>418</v>
@@ -13310,13 +13340,13 @@
         <v>242</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>419</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>420</v>
@@ -13333,13 +13363,13 @@
         <v>247</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>421</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>422</v>
@@ -13356,13 +13386,13 @@
         <v>250</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>423</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>424</v>
@@ -13379,13 +13409,13 @@
         <v>253</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>425</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>426</v>
@@ -13408,7 +13438,7 @@
         <v>427</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>428</v>
@@ -13425,13 +13455,13 @@
         <v>259</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>429</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>430</v>
@@ -13448,13 +13478,13 @@
         <v>262</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>431</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>432</v>
@@ -13471,13 +13501,13 @@
         <v>265</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>433</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>434</v>
@@ -13494,13 +13524,13 @@
         <v>268</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>435</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>436</v>
@@ -13517,13 +13547,13 @@
         <v>271</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>437</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>438</v>
@@ -13540,13 +13570,13 @@
         <v>274</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>439</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>440</v>
@@ -13563,13 +13593,13 @@
         <v>277</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>441</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>442</v>
@@ -13609,13 +13639,13 @@
         <v>283</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>445</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>446</v>
@@ -13632,13 +13662,13 @@
         <v>286</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>447</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>448</v>
@@ -13655,13 +13685,13 @@
         <v>289</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>449</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>450</v>
@@ -13678,13 +13708,13 @@
         <v>292</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>451</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>452</v>
@@ -13701,13 +13731,13 @@
         <v>295</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>453</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>454</v>
@@ -13724,13 +13754,13 @@
         <v>298</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>455</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>456</v>
@@ -13747,13 +13777,13 @@
         <v>301</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>457</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>458</v>
@@ -13770,13 +13800,13 @@
         <v>304</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>459</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>460</v>
@@ -13793,13 +13823,13 @@
         <v>307</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>461</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>462</v>
@@ -13816,7 +13846,7 @@
         <v>310</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>463</v>
@@ -13839,7 +13869,7 @@
         <v>313</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>465</v>
@@ -13862,13 +13892,13 @@
         <v>316</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>467</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>468</v>
@@ -13885,13 +13915,13 @@
         <v>242</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>469</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>470</v>
@@ -13908,13 +13938,13 @@
         <v>247</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>471</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>472</v>
@@ -13931,13 +13961,13 @@
         <v>250</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>473</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>474</v>
@@ -13954,13 +13984,13 @@
         <v>253</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>475</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>476</v>
@@ -13983,7 +14013,7 @@
         <v>477</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>478</v>
@@ -14000,13 +14030,13 @@
         <v>259</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>479</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>480</v>
@@ -14023,13 +14053,13 @@
         <v>262</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>481</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>482</v>
@@ -14046,13 +14076,13 @@
         <v>265</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>483</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>484</v>
@@ -14069,13 +14099,13 @@
         <v>268</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>485</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>486</v>
@@ -14092,13 +14122,13 @@
         <v>271</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>487</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>488</v>
@@ -14115,13 +14145,13 @@
         <v>274</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>489</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>490</v>
@@ -14138,13 +14168,13 @@
         <v>277</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>491</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>492</v>
@@ -14184,13 +14214,13 @@
         <v>283</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>495</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>496</v>
@@ -14207,13 +14237,13 @@
         <v>286</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>497</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>498</v>
@@ -14230,13 +14260,13 @@
         <v>289</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>499</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>500</v>
@@ -14253,13 +14283,13 @@
         <v>292</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>501</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>502</v>
@@ -14276,13 +14306,13 @@
         <v>295</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>503</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>504</v>
@@ -14299,13 +14329,13 @@
         <v>298</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>505</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>506</v>
@@ -14322,13 +14352,13 @@
         <v>301</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>507</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>508</v>
@@ -14345,13 +14375,13 @@
         <v>304</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>509</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>510</v>
@@ -14368,13 +14398,13 @@
         <v>307</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>511</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>512</v>
@@ -14391,7 +14421,7 @@
         <v>310</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>513</v>
@@ -14414,7 +14444,7 @@
         <v>313</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>515</v>
@@ -14437,13 +14467,13 @@
         <v>316</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>517</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>518</v>
@@ -14460,13 +14490,13 @@
         <v>242</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>519</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>520</v>
@@ -14483,13 +14513,13 @@
         <v>247</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>521</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>522</v>
@@ -14506,13 +14536,13 @@
         <v>250</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>523</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>524</v>
@@ -14529,13 +14559,13 @@
         <v>253</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>525</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>526</v>
@@ -14558,7 +14588,7 @@
         <v>527</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>528</v>
@@ -14575,13 +14605,13 @@
         <v>259</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>529</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>530</v>
@@ -14598,13 +14628,13 @@
         <v>262</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>531</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>532</v>
@@ -14621,13 +14651,13 @@
         <v>265</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>533</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>534</v>
@@ -14644,13 +14674,13 @@
         <v>268</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>535</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>536</v>
@@ -14667,13 +14697,13 @@
         <v>271</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>537</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>538</v>
@@ -14690,13 +14720,13 @@
         <v>274</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>539</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>540</v>
@@ -14713,13 +14743,13 @@
         <v>277</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>541</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>542</v>
@@ -14759,13 +14789,13 @@
         <v>283</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>545</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>546</v>
@@ -14782,13 +14812,13 @@
         <v>286</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>547</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>548</v>
@@ -14805,13 +14835,13 @@
         <v>289</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>549</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>550</v>
@@ -14828,13 +14858,13 @@
         <v>292</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>551</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>552</v>
@@ -14851,13 +14881,13 @@
         <v>295</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>553</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>554</v>
@@ -14874,13 +14904,13 @@
         <v>298</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>555</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>556</v>
@@ -14897,13 +14927,13 @@
         <v>301</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>557</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>558</v>
@@ -14920,13 +14950,13 @@
         <v>304</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>559</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>560</v>
@@ -14943,13 +14973,13 @@
         <v>307</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>561</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>562</v>
@@ -14966,7 +14996,7 @@
         <v>310</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>563</v>
@@ -14989,7 +15019,7 @@
         <v>313</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>565</v>
@@ -15012,13 +15042,13 @@
         <v>316</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>567</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>568</v>
@@ -15035,13 +15065,13 @@
         <v>242</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>569</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>570</v>
@@ -15058,13 +15088,13 @@
         <v>247</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>571</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>572</v>
@@ -15081,13 +15111,13 @@
         <v>250</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>573</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>574</v>
@@ -15104,13 +15134,13 @@
         <v>253</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>575</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>576</v>
@@ -15133,7 +15163,7 @@
         <v>577</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>578</v>
@@ -15150,13 +15180,13 @@
         <v>259</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>579</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>580</v>
@@ -15173,13 +15203,13 @@
         <v>262</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>581</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>582</v>
@@ -15196,13 +15226,13 @@
         <v>265</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>583</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>584</v>
@@ -15219,13 +15249,13 @@
         <v>268</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>585</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>586</v>
@@ -15242,13 +15272,13 @@
         <v>271</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>587</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>588</v>
@@ -15265,13 +15295,13 @@
         <v>274</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>589</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>590</v>
@@ -15288,13 +15318,13 @@
         <v>277</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>592</v>
@@ -15334,13 +15364,13 @@
         <v>283</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>595</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>596</v>
@@ -15357,13 +15387,13 @@
         <v>286</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>597</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>598</v>
@@ -15380,13 +15410,13 @@
         <v>289</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>599</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>600</v>
@@ -15403,13 +15433,13 @@
         <v>292</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>601</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>602</v>
@@ -15426,13 +15456,13 @@
         <v>295</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>603</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>604</v>
@@ -15449,13 +15479,13 @@
         <v>298</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>605</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>606</v>
@@ -15472,13 +15502,13 @@
         <v>301</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>607</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>608</v>
@@ -15495,13 +15525,13 @@
         <v>304</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>609</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>610</v>
@@ -15518,13 +15548,13 @@
         <v>307</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>611</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>612</v>
@@ -15541,7 +15571,7 @@
         <v>310</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>613</v>
@@ -15564,7 +15594,7 @@
         <v>313</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>615</v>
@@ -15587,13 +15617,13 @@
         <v>316</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>617</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>618</v>
@@ -15616,11 +15646,11 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:CV152"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.73828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.3359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="15.53515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.25390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="5.859375" customWidth="true"/>
     <col min="4" max="4" width="5.859375" customWidth="true"/>
     <col min="5" max="5" width="5.859375" customWidth="true"/>
@@ -17562,7 +17592,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="7">
     <mergeCell ref="C1:P1"/>
     <mergeCell ref="Q1:AD1"/>
     <mergeCell ref="AE1:AR1"/>
@@ -17581,12 +17611,16 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.08203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="20.46484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="17.2734375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.34765625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="6.08984375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="1.015625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="12.08984375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="12.73046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17608,26 +17642,31 @@
       <c r="C3" s="1" t="s">
         <v>638</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>641</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="n">
+        <v>-875.0</v>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
